--- a/Dataset/contract analysis table.xlsx
+++ b/Dataset/contract analysis table.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\고려대학교\논문 작업\Value Range Inference\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\isjeon\PycharmProjects\pythonProject\SolidityGuardian\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BE2BDD-AAA0-411F-A474-9DFC27983847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56FF91F-24FA-48B8-B140-BDFC0D677389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF54B6F5-4224-47EB-99B3-226B36AF4834}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FF54B6F5-4224-47EB-99B3-226B36AF4834}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="테이블" sheetId="1" r:id="rId1"/>
+    <sheet name="교체" sheetId="2" r:id="rId2"/>
+    <sheet name="함수 이름 같은 것" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="280">
   <si>
     <t>Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,10 +56,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>constructor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>testing comment essential</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -477,10 +474,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>uint, int, bool에 대해 주석을 달 필요가 없는 코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>fairLaunchDeposit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -604,10 +597,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>_tramsfer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>uint _amount, mapping(address =&gt; uint256) private _balances</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -644,6 +633,522 @@
   </si>
   <si>
     <t>거의 interface</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_authorizeUgrade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint amount, mapping(address =&gt; mapping(address =&gt; uint256)) _allowances</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>burnFrom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_transfer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blacklistUser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mapping (address =&gt; bool) public blacklisted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeFromBlacklist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>includeInRAMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mapping (address =&gt; bool) public execludedFromRAMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excludeFromRAMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>includeInLTAF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mapping(address=&gt;bool) public includedInLTAF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excludedFromLTAF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>updateLtafPercentage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint256 percentage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pauseContract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unPauseContract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>withdrawBNBFromContract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>withdrawToken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mapping (address =&gt; bool) public blacklisted, mapping(address=&gt;bool) public includedInLTAF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파일 이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>함수 이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>updateUserInfo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint256 year, uint256 month, block.timestamp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_mint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_burn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>addLevls</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AprOracle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCompoundBorrowIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>block.number 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getAaveBorrowIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getAverageDailyRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>capture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCompoundBorrowIndex, getAaveBorrowIndex에 의한 multi contract transaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라이브러리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>library</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AstridMath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATIDStaking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setAddresses</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로직 없는 할당문 및 함수 호출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_insertLockedStake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_removeLockedStake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint _lockedStakeID, 구조체 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stakeLocked</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unstakeLocked</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint _stakeWeight, uint _lockedUntil, 구조체 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint _ATIDamount, uint _lockedUntil, 구조체 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>increaseF_COL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint _COLFee 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>increaseF_BAI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getPendingCOLGain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_getPendingCOLGain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mapping 때문에 address에 대한 testing 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getPendingBAIGain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_getStakeWeight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_getPendingBAIGain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint _lockedUntil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_updateUserSnapshots</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_sendCOLGainToUser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool success</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_requireCallerIsVaultManager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>require문 한 개 (다른 함수에서 호출)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_requireCallerIsBorrowerOperations</t>
+  </si>
+  <si>
+    <t>_requireCallerIsActivePool</t>
+  </si>
+  <si>
+    <t>_requireUserHasStake</t>
+  </si>
+  <si>
+    <t>_requireNonZeroAmount</t>
+  </si>
+  <si>
+    <t>receive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Audius</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_deposit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint _amount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다른 컨트랙트 상속받아 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_stake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_unstake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>processUnstake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint _amount 쓰긴 하는데 직접적인 영향 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">_withdraw </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로직 없는 할당, 함수 호출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>processWithdraw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_claimRewards</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint256 stake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_processNewStake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint256 _newStake 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_setStakingContract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AuthorizationUtils</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Balancer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_authorizeUpgrade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setMar2Market</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setActionBuilders</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>address.length testing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>addActionBuilderAt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_addActionBuilderAt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buildBalanceActions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15kb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseCurveConvex4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseCurveConvex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setZunami</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getZunamiLpInStrat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>totalHoldings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testing 할건 각종 상태변수 및 balanceOf 같은 것들</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>withdraw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>claimManagementFees</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setCrvCvx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setExtraToken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sellToken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>withdrawAll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testing 할건 각종 상태변수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>updateMinDepositAmount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint _minDepositAmount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>굳이 testing 안해도 됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>updateZumaniLpInStrat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코드 이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abstract contract</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseJumpRateModeV2.sol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseReactorStroage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>함수가 없고 상태변수만 있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BNLPFactory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createNewNode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint amount가 있긴 하나 상관이 없음 주로 address</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whitelistToken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bankingNodeCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BNPLRewardsController</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비슷한 컨트랙트 한번 해서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12kb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BoringERC20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BoringRebase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BorrowLogic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11kb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BridgeLogic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bufferstaking</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1031,10 +1536,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F6AB7A-DC19-46CC-839B-BEB515A848FD}">
-  <dimension ref="B3:O83"/>
+  <dimension ref="B3:O165"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.69921875" customWidth="1"/>
     <col min="4" max="4" width="14.8984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.09765625" bestFit="1" customWidth="1"/>
@@ -1048,104 +1553,107 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="N3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B4" s="1"/>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>8</v>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>8</v>
+      <c r="F5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="I5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" t="s">
-        <v>8</v>
-      </c>
-      <c r="M5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1157,26 +1665,15 @@
         <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>42</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B7" s="1"/>
@@ -1186,10 +1683,10 @@
         <v>18</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1201,10 +1698,10 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
         <v>95</v>
@@ -1222,10 +1719,10 @@
         <v>21</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1237,40 +1734,51 @@
         <v>22</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.4">
       <c r="F11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>97</v>
+        <v>7</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.4">
@@ -1278,36 +1786,25 @@
         <v>23</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>43</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>95</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.4">
       <c r="F13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1319,10 +1816,10 @@
         <v>25</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1331,156 +1828,156 @@
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.4">
       <c r="F15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" t="s">
-        <v>96</v>
-      </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.4">
       <c r="F16" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F17" s="1" t="s">
         <v>31</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" t="s">
-        <v>96</v>
-      </c>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="I17" t="s">
+        <v>7</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" t="s">
+        <v>7</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="C19" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="D19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
       <c r="F19" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I19" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>95</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
     </row>
     <row r="20" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" t="s">
-        <v>34</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>95</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
     </row>
     <row r="21" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" t="s">
-        <v>96</v>
-      </c>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="22" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F22" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1489,115 +1986,124 @@
     </row>
     <row r="23" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F23" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F24" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" t="s">
-        <v>96</v>
-      </c>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="25" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F25" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I25" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>44</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>94</v>
+      </c>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
     </row>
     <row r="26" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F26" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I26" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>98</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>94</v>
+      </c>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
     </row>
     <row r="27" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F27" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H27" t="s">
-        <v>95</v>
-      </c>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="I27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="28" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="C28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" t="s">
+        <v>61</v>
+      </c>
       <c r="F28" s="1" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
         <v>95</v>
@@ -1609,68 +2115,43 @@
     </row>
     <row r="29" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F29" s="1" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H29" t="s">
+        <v>95</v>
+      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
     </row>
     <row r="30" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C30" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" t="s">
-        <v>62</v>
-      </c>
-      <c r="E30" t="s">
-        <v>62</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I30" t="s">
-        <v>8</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
     </row>
     <row r="31" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F31" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -1679,13 +2160,13 @@
     </row>
     <row r="32" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F32" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -1694,1020 +2175,2767 @@
     </row>
     <row r="33" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F33" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="I33" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="C34" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" t="s">
+        <v>72</v>
+      </c>
       <c r="F34" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H34" t="s">
-        <v>96</v>
-      </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="I34" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F35" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H35" t="s">
-        <v>96</v>
-      </c>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="I35" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F36" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>71</v>
+        <v>7</v>
+      </c>
+      <c r="N36" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="3:14" x14ac:dyDescent="0.4">
-      <c r="C37" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" t="s">
-        <v>73</v>
-      </c>
-      <c r="E37" t="s">
-        <v>73</v>
-      </c>
       <c r="F37" s="1" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I37" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F38" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F39" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F40" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I40" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N40" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F41" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I41" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F42" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F43" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I43" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F44" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I44" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F45" s="1" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F46" s="1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F47" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="3:14" x14ac:dyDescent="0.4">
       <c r="F48" s="1" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F49" s="1" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>100</v>
+        <v>7</v>
+      </c>
+      <c r="N49" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F50" s="1" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I50" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>102</v>
+        <v>7</v>
+      </c>
+      <c r="N50" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="C51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" t="s">
+        <v>108</v>
+      </c>
       <c r="F51" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I51" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>105</v>
+        <v>7</v>
+      </c>
+      <c r="N51" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F52" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I52" t="s">
-        <v>8</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L52" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>106</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H52" t="s">
+        <v>95</v>
+      </c>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
     </row>
     <row r="53" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F53" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I53" t="s">
-        <v>16</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N53" t="s">
-        <v>107</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H53" t="s">
+        <v>95</v>
+      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
     </row>
     <row r="54" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F54" s="1" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N54" t="s">
-        <v>108</v>
+        <v>7</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C55" t="s">
-        <v>54</v>
-      </c>
-      <c r="D55" t="s">
-        <v>109</v>
-      </c>
-      <c r="E55" t="s">
-        <v>109</v>
-      </c>
       <c r="F55" s="1" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I55" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F56" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N56" t="s">
-        <v>112</v>
+        <v>7</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="C57" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57" t="s">
+        <v>117</v>
+      </c>
+      <c r="E57" t="s">
+        <v>117</v>
+      </c>
       <c r="F57" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>96</v>
-      </c>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
+        <v>94</v>
+      </c>
     </row>
     <row r="58" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F58" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H58" t="s">
-        <v>96</v>
-      </c>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
+        <v>94</v>
+      </c>
     </row>
     <row r="59" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F59" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I59" t="s">
-        <v>16</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M59" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O59" s="1" t="s">
-        <v>117</v>
+        <v>15</v>
+      </c>
+      <c r="H59" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F60" s="1" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I60" t="s">
-        <v>8</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M60" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>117</v>
+        <v>15</v>
+      </c>
+      <c r="H60" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F61" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I61" t="s">
-        <v>16</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M61" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>117</v>
+        <v>15</v>
+      </c>
+      <c r="H61" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="C62" t="s">
-        <v>118</v>
-      </c>
-      <c r="D62" t="s">
-        <v>119</v>
-      </c>
-      <c r="E62" t="s">
-        <v>119</v>
-      </c>
       <c r="F62" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H62" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F63" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="3:15" x14ac:dyDescent="0.4">
       <c r="F64" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="65" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F65" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="66" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F66" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F67" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I67" t="s">
+        <v>7</v>
+      </c>
+      <c r="J67" t="s">
+        <v>14</v>
+      </c>
+      <c r="K67" t="s">
+        <v>15</v>
+      </c>
+      <c r="L67" t="s">
+        <v>7</v>
+      </c>
+      <c r="M67" t="s">
+        <v>15</v>
+      </c>
+      <c r="N67" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="68" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F68" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I68" t="s">
+        <v>7</v>
+      </c>
+      <c r="J68" t="s">
+        <v>14</v>
+      </c>
+      <c r="K68" t="s">
+        <v>15</v>
+      </c>
+      <c r="L68" t="s">
+        <v>7</v>
+      </c>
+      <c r="M68" t="s">
+        <v>15</v>
+      </c>
+      <c r="N68" t="s">
+        <v>135</v>
+      </c>
+      <c r="O68" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="69" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F69" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I69" t="s">
+        <v>7</v>
+      </c>
+      <c r="J69" t="s">
+        <v>137</v>
+      </c>
+      <c r="K69" t="s">
+        <v>15</v>
+      </c>
+      <c r="L69" t="s">
+        <v>7</v>
+      </c>
+      <c r="M69" t="s">
+        <v>15</v>
+      </c>
+      <c r="N69" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="70" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F70" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I70" t="s">
+        <v>7</v>
+      </c>
+      <c r="J70" t="s">
+        <v>14</v>
+      </c>
+      <c r="K70" t="s">
+        <v>15</v>
+      </c>
+      <c r="L70" t="s">
+        <v>15</v>
+      </c>
+      <c r="M70" t="s">
+        <v>15</v>
+      </c>
+      <c r="N70" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F71" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="72" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F72" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I72" t="s">
+        <v>7</v>
+      </c>
+      <c r="J72" t="s">
+        <v>14</v>
+      </c>
+      <c r="K72" t="s">
+        <v>15</v>
+      </c>
+      <c r="L72" t="s">
+        <v>15</v>
+      </c>
+      <c r="M72" t="s">
+        <v>15</v>
+      </c>
+      <c r="N72" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="73" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F73" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F74" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="C75" t="s">
+        <v>147</v>
+      </c>
+      <c r="D75" t="s">
+        <v>148</v>
+      </c>
+      <c r="E75" t="s">
+        <v>148</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="76" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F76" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="77" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F77" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H64" t="s">
+      <c r="G77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="78" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F78" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="79" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F79" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F80" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="81" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F81" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="82" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F82" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="83" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F83" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="84" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F84" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I84" t="s">
+        <v>7</v>
+      </c>
+      <c r="J84" t="s">
+        <v>14</v>
+      </c>
+      <c r="K84" t="s">
+        <v>15</v>
+      </c>
+      <c r="L84" t="s">
+        <v>7</v>
+      </c>
+      <c r="M84" t="s">
+        <v>15</v>
+      </c>
+      <c r="N84" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="85" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F85" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I85" t="s">
+        <v>7</v>
+      </c>
+      <c r="J85" t="s">
+        <v>14</v>
+      </c>
+      <c r="K85" t="s">
+        <v>15</v>
+      </c>
+      <c r="L85" t="s">
+        <v>7</v>
+      </c>
+      <c r="M85" t="s">
+        <v>15</v>
+      </c>
+      <c r="N85" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="86" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F86" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I86" t="s">
+        <v>7</v>
+      </c>
+      <c r="J86" t="s">
+        <v>137</v>
+      </c>
+      <c r="K86" t="s">
+        <v>15</v>
+      </c>
+      <c r="L86" t="s">
+        <v>7</v>
+      </c>
+      <c r="M86" t="s">
+        <v>15</v>
+      </c>
+      <c r="N86" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="87" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F87" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="88" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F88" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I88" t="s">
+        <v>7</v>
+      </c>
+      <c r="J88" t="s">
+        <v>14</v>
+      </c>
+      <c r="K88" t="s">
+        <v>15</v>
+      </c>
+      <c r="L88" t="s">
+        <v>7</v>
+      </c>
+      <c r="M88" t="s">
+        <v>15</v>
+      </c>
+      <c r="N88" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="89" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F89" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I89" t="s">
+        <v>7</v>
+      </c>
+      <c r="J89" t="s">
+        <v>11</v>
+      </c>
+      <c r="K89" t="s">
+        <v>7</v>
+      </c>
+      <c r="L89" t="s">
+        <v>7</v>
+      </c>
+      <c r="M89" t="s">
+        <v>7</v>
+      </c>
+      <c r="N89" t="s">
+        <v>155</v>
+      </c>
+      <c r="O89" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="90" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F90" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I90" t="s">
+        <v>7</v>
+      </c>
+      <c r="J90" t="s">
+        <v>11</v>
+      </c>
+      <c r="K90" t="s">
+        <v>7</v>
+      </c>
+      <c r="L90" t="s">
+        <v>7</v>
+      </c>
+      <c r="M90" t="s">
+        <v>7</v>
+      </c>
+      <c r="N90" t="s">
+        <v>155</v>
+      </c>
+      <c r="O90" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="91" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F91" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I91" t="s">
+        <v>7</v>
+      </c>
+      <c r="J91" t="s">
+        <v>11</v>
+      </c>
+      <c r="K91" t="s">
+        <v>7</v>
+      </c>
+      <c r="L91" t="s">
+        <v>7</v>
+      </c>
+      <c r="M91" t="s">
+        <v>7</v>
+      </c>
+      <c r="N91" t="s">
+        <v>158</v>
+      </c>
+      <c r="O91" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="92" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F92" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I92" t="s">
+        <v>7</v>
+      </c>
+      <c r="J92" t="s">
+        <v>11</v>
+      </c>
+      <c r="K92" t="s">
+        <v>7</v>
+      </c>
+      <c r="L92" t="s">
+        <v>7</v>
+      </c>
+      <c r="M92" t="s">
+        <v>7</v>
+      </c>
+      <c r="N92" t="s">
+        <v>158</v>
+      </c>
+      <c r="O92" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="93" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F93" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I93" t="s">
+        <v>7</v>
+      </c>
+      <c r="J93" t="s">
+        <v>11</v>
+      </c>
+      <c r="K93" t="s">
+        <v>7</v>
+      </c>
+      <c r="L93" t="s">
+        <v>7</v>
+      </c>
+      <c r="M93" t="s">
+        <v>7</v>
+      </c>
+      <c r="N93" t="s">
+        <v>161</v>
+      </c>
+      <c r="O93" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="94" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F94" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I94" t="s">
+        <v>7</v>
+      </c>
+      <c r="J94" t="s">
+        <v>11</v>
+      </c>
+      <c r="K94" t="s">
+        <v>7</v>
+      </c>
+      <c r="L94" t="s">
+        <v>7</v>
+      </c>
+      <c r="M94" t="s">
+        <v>7</v>
+      </c>
+      <c r="N94" t="s">
+        <v>161</v>
+      </c>
+      <c r="O94" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="95" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F95" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I95" t="s">
+        <v>7</v>
+      </c>
+      <c r="J95" t="s">
+        <v>14</v>
+      </c>
+      <c r="K95" t="s">
+        <v>7</v>
+      </c>
+      <c r="L95" t="s">
+        <v>7</v>
+      </c>
+      <c r="M95" t="s">
+        <v>7</v>
+      </c>
+      <c r="N95" t="s">
+        <v>164</v>
+      </c>
+      <c r="O95" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="96" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F96" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H96" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="65" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F65" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H65" t="s">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F97" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="66" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F66" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H66" t="s">
+    <row r="98" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F98" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I98" t="s">
+        <v>7</v>
+      </c>
+      <c r="J98" t="s">
+        <v>14</v>
+      </c>
+      <c r="K98" t="s">
+        <v>15</v>
+      </c>
+      <c r="L98" t="s">
+        <v>7</v>
+      </c>
+      <c r="M98" t="s">
+        <v>7</v>
+      </c>
+      <c r="N98" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F99" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I99" t="s">
+        <v>15</v>
+      </c>
+      <c r="J99" t="s">
+        <v>14</v>
+      </c>
+      <c r="K99" t="s">
+        <v>15</v>
+      </c>
+      <c r="L99" t="s">
+        <v>7</v>
+      </c>
+      <c r="M99" t="s">
+        <v>7</v>
+      </c>
+      <c r="N99" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F100" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J100" t="s">
+        <v>14</v>
+      </c>
+      <c r="K100" t="s">
+        <v>15</v>
+      </c>
+      <c r="L100" t="s">
+        <v>15</v>
+      </c>
+      <c r="M100" t="s">
+        <v>15</v>
+      </c>
+      <c r="N100" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F101" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J101" t="s">
+        <v>11</v>
+      </c>
+      <c r="K101" t="s">
+        <v>15</v>
+      </c>
+      <c r="L101" t="s">
+        <v>7</v>
+      </c>
+      <c r="M101" t="s">
+        <v>7</v>
+      </c>
+      <c r="N101" t="s">
+        <v>169</v>
+      </c>
+      <c r="O101" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F102" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I102" t="s">
+        <v>7</v>
+      </c>
+      <c r="J102" t="s">
+        <v>14</v>
+      </c>
+      <c r="K102" t="s">
+        <v>15</v>
+      </c>
+      <c r="L102" t="s">
+        <v>7</v>
+      </c>
+      <c r="M102" t="s">
+        <v>7</v>
+      </c>
+      <c r="N102" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="103" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F103" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I103" t="s">
+        <v>7</v>
+      </c>
+      <c r="J103" t="s">
+        <v>14</v>
+      </c>
+      <c r="K103" t="s">
+        <v>15</v>
+      </c>
+      <c r="L103" t="s">
+        <v>7</v>
+      </c>
+      <c r="M103" t="s">
+        <v>15</v>
+      </c>
+      <c r="N103" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="104" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F104" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I104" t="s">
+        <v>7</v>
+      </c>
+      <c r="J104" t="s">
+        <v>14</v>
+      </c>
+      <c r="K104" t="s">
+        <v>15</v>
+      </c>
+      <c r="L104" t="s">
+        <v>7</v>
+      </c>
+      <c r="M104" t="s">
+        <v>15</v>
+      </c>
+      <c r="N104" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="105" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F105" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="106" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F106" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="107" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="C107" t="s">
+        <v>60</v>
+      </c>
+      <c r="D107" t="s">
+        <v>178</v>
+      </c>
+      <c r="E107" t="s">
+        <v>178</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I107" t="s">
+        <v>15</v>
+      </c>
+      <c r="J107" t="s">
+        <v>14</v>
+      </c>
+      <c r="K107" t="s">
+        <v>15</v>
+      </c>
+      <c r="L107" t="s">
+        <v>7</v>
+      </c>
+      <c r="M107" t="s">
+        <v>15</v>
+      </c>
+      <c r="N107" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="108" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F108" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="67" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F67" s="1" t="s">
+    <row r="109" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F109" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I109" t="s">
+        <v>15</v>
+      </c>
+      <c r="J109" t="s">
+        <v>14</v>
+      </c>
+      <c r="K109" t="s">
+        <v>15</v>
+      </c>
+      <c r="L109" t="s">
+        <v>7</v>
+      </c>
+      <c r="M109" t="s">
+        <v>15</v>
+      </c>
+      <c r="N109" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="110" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F110" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I110" t="s">
+        <v>15</v>
+      </c>
+      <c r="J110" t="s">
+        <v>14</v>
+      </c>
+      <c r="K110" t="s">
+        <v>15</v>
+      </c>
+      <c r="L110" t="s">
+        <v>15</v>
+      </c>
+      <c r="M110" t="s">
+        <v>15</v>
+      </c>
+      <c r="N110" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="111" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="C111" t="s">
+        <v>59</v>
+      </c>
+      <c r="D111" t="s">
+        <v>188</v>
+      </c>
+      <c r="E111" t="s">
+        <v>188</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H111" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="112" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F112" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I112" t="s">
+        <v>7</v>
+      </c>
+      <c r="J112" t="s">
+        <v>14</v>
+      </c>
+      <c r="K112" t="s">
+        <v>15</v>
+      </c>
+      <c r="L112" t="s">
+        <v>7</v>
+      </c>
+      <c r="M112" t="s">
+        <v>15</v>
+      </c>
+      <c r="N112" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="113" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F113" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I113" t="s">
+        <v>7</v>
+      </c>
+      <c r="J113" t="s">
+        <v>14</v>
+      </c>
+      <c r="K113" t="s">
+        <v>15</v>
+      </c>
+      <c r="L113" t="s">
+        <v>7</v>
+      </c>
+      <c r="M113" t="s">
+        <v>15</v>
+      </c>
+      <c r="N113" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="114" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F114" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I114" t="s">
+        <v>7</v>
+      </c>
+      <c r="J114" t="s">
+        <v>14</v>
+      </c>
+      <c r="K114" t="s">
+        <v>15</v>
+      </c>
+      <c r="L114" t="s">
+        <v>7</v>
+      </c>
+      <c r="M114" t="s">
+        <v>15</v>
+      </c>
+      <c r="N114" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="115" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F115" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I115" t="s">
+        <v>7</v>
+      </c>
+      <c r="J115" t="s">
+        <v>14</v>
+      </c>
+      <c r="K115" t="s">
+        <v>15</v>
+      </c>
+      <c r="L115" t="s">
+        <v>7</v>
+      </c>
+      <c r="M115" t="s">
+        <v>15</v>
+      </c>
+      <c r="N115" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="116" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F116" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I116" t="s">
+        <v>7</v>
+      </c>
+      <c r="J116" t="s">
+        <v>14</v>
+      </c>
+      <c r="K116" t="s">
+        <v>15</v>
+      </c>
+      <c r="L116" t="s">
+        <v>7</v>
+      </c>
+      <c r="M116" t="s">
+        <v>15</v>
+      </c>
+      <c r="N116" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="117" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F117" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I117" t="s">
+        <v>7</v>
+      </c>
+      <c r="J117" t="s">
+        <v>14</v>
+      </c>
+      <c r="K117" t="s">
+        <v>15</v>
+      </c>
+      <c r="L117" t="s">
+        <v>7</v>
+      </c>
+      <c r="M117" t="s">
+        <v>15</v>
+      </c>
+      <c r="N117" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="118" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F118" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H118" t="s">
         <v>127</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H67" t="s">
+    </row>
+    <row r="119" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F119" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I119" t="s">
+        <v>7</v>
+      </c>
+      <c r="J119" t="s">
+        <v>14</v>
+      </c>
+      <c r="K119" t="s">
+        <v>15</v>
+      </c>
+      <c r="L119" t="s">
+        <v>7</v>
+      </c>
+      <c r="M119" t="s">
+        <v>7</v>
+      </c>
+      <c r="O119" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="120" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F120" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H120" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="121" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F121" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I121" t="s">
+        <v>7</v>
+      </c>
+      <c r="J121" t="s">
+        <v>14</v>
+      </c>
+      <c r="K121" t="s">
+        <v>15</v>
+      </c>
+      <c r="L121" t="s">
+        <v>7</v>
+      </c>
+      <c r="M121" t="s">
+        <v>7</v>
+      </c>
+      <c r="O121" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="122" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F122" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I122" t="s">
+        <v>7</v>
+      </c>
+      <c r="J122" t="s">
+        <v>14</v>
+      </c>
+      <c r="K122" t="s">
+        <v>15</v>
+      </c>
+      <c r="L122" t="s">
+        <v>15</v>
+      </c>
+      <c r="M122" t="s">
+        <v>15</v>
+      </c>
+      <c r="N122" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="123" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F123" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H123" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="124" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F124" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H124" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="68" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F68" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H68" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="69" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F69" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H69" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="70" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F70" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H70" t="s">
+      <c r="J124" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="125" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F125" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I125" t="s">
+        <v>7</v>
+      </c>
+      <c r="J125" t="s">
+        <v>11</v>
+      </c>
+      <c r="K125" t="s">
+        <v>7</v>
+      </c>
+      <c r="L125" t="s">
+        <v>7</v>
+      </c>
+      <c r="M125" t="s">
+        <v>7</v>
+      </c>
+      <c r="N125" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="126" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F126" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H126" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="127" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F127" t="s">
+        <v>213</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H127" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="128" spans="6:15" x14ac:dyDescent="0.4">
+      <c r="F128" t="s">
+        <v>214</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H128" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="129" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F129" t="s">
+        <v>215</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="130" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F130" t="s">
+        <v>216</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H130" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="131" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F131" t="s">
+        <v>217</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H131" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="71" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F71" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H71" t="s">
+    <row r="132" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="C132" t="s">
+        <v>32</v>
+      </c>
+      <c r="D132" t="s">
+        <v>218</v>
+      </c>
+      <c r="E132" t="s">
+        <v>218</v>
+      </c>
+      <c r="F132" t="s">
+        <v>63</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="133" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F133" t="s">
+        <v>219</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I133" t="s">
+        <v>15</v>
+      </c>
+      <c r="J133" t="s">
+        <v>14</v>
+      </c>
+      <c r="K133" t="s">
+        <v>15</v>
+      </c>
+      <c r="L133" t="s">
+        <v>7</v>
+      </c>
+      <c r="M133" t="s">
+        <v>15</v>
+      </c>
+      <c r="N133" t="s">
+        <v>220</v>
+      </c>
+      <c r="O133" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="134" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F134" t="s">
+        <v>222</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I134" t="s">
+        <v>15</v>
+      </c>
+      <c r="J134" t="s">
+        <v>14</v>
+      </c>
+      <c r="K134" t="s">
+        <v>15</v>
+      </c>
+      <c r="L134" t="s">
+        <v>15</v>
+      </c>
+      <c r="M134" t="s">
+        <v>15</v>
+      </c>
+      <c r="N134" t="s">
+        <v>220</v>
+      </c>
+      <c r="O134" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="135" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F135" t="s">
+        <v>223</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I135" t="s">
+        <v>15</v>
+      </c>
+      <c r="J135" t="s">
+        <v>14</v>
+      </c>
+      <c r="K135" t="s">
+        <v>15</v>
+      </c>
+      <c r="L135" t="s">
+        <v>15</v>
+      </c>
+      <c r="M135" t="s">
+        <v>15</v>
+      </c>
+      <c r="N135" t="s">
+        <v>220</v>
+      </c>
+      <c r="O135" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="136" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F136" t="s">
+        <v>224</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I136" t="s">
+        <v>15</v>
+      </c>
+      <c r="J136" t="s">
+        <v>7</v>
+      </c>
+      <c r="K136" t="s">
+        <v>7</v>
+      </c>
+      <c r="L136" t="s">
+        <v>7</v>
+      </c>
+      <c r="M136" t="s">
+        <v>7</v>
+      </c>
+      <c r="N136" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="137" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F137" t="s">
+        <v>226</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H137" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="138" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F138" t="s">
+        <v>228</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I138" t="s">
+        <v>15</v>
+      </c>
+      <c r="J138" t="s">
+        <v>14</v>
+      </c>
+      <c r="K138" t="s">
+        <v>15</v>
+      </c>
+      <c r="L138" t="s">
+        <v>7</v>
+      </c>
+      <c r="M138" t="s">
+        <v>15</v>
+      </c>
+      <c r="N138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="139" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F139" t="s">
+        <v>229</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I139" t="s">
+        <v>15</v>
+      </c>
+      <c r="J139" t="s">
+        <v>14</v>
+      </c>
+      <c r="K139" t="s">
+        <v>7</v>
+      </c>
+      <c r="L139" t="s">
+        <v>7</v>
+      </c>
+      <c r="M139" t="s">
+        <v>7</v>
+      </c>
+      <c r="N139" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="140" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F140" t="s">
+        <v>231</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I140" t="s">
+        <v>15</v>
+      </c>
+      <c r="J140" t="s">
+        <v>14</v>
+      </c>
+      <c r="K140" t="s">
+        <v>15</v>
+      </c>
+      <c r="L140" t="s">
+        <v>15</v>
+      </c>
+      <c r="M140" t="s">
+        <v>15</v>
+      </c>
+      <c r="N140" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="141" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F141" t="s">
+        <v>233</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H141" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="72" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F72" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H72" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="73" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F73" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I73" t="s">
-        <v>8</v>
-      </c>
-      <c r="J73" t="s">
-        <v>15</v>
-      </c>
-      <c r="K73" t="s">
-        <v>16</v>
-      </c>
-      <c r="L73" t="s">
-        <v>16</v>
-      </c>
-      <c r="M73" t="s">
-        <v>8</v>
-      </c>
-      <c r="N73" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="74" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F74" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I74" t="s">
-        <v>8</v>
-      </c>
-      <c r="J74" t="s">
-        <v>15</v>
-      </c>
-      <c r="K74" t="s">
-        <v>16</v>
-      </c>
-      <c r="L74" t="s">
-        <v>8</v>
-      </c>
-      <c r="M74" t="s">
-        <v>16</v>
-      </c>
-      <c r="N74" t="s">
-        <v>137</v>
-      </c>
-      <c r="O74" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="75" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F75" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I75" t="s">
-        <v>8</v>
-      </c>
-      <c r="J75" t="s">
-        <v>139</v>
-      </c>
-      <c r="K75" t="s">
-        <v>16</v>
-      </c>
-      <c r="L75" t="s">
-        <v>16</v>
-      </c>
-      <c r="M75" t="s">
-        <v>8</v>
-      </c>
-      <c r="N75" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="76" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F76" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I76" t="s">
-        <v>8</v>
-      </c>
-      <c r="J76" t="s">
-        <v>15</v>
-      </c>
-      <c r="K76" t="s">
-        <v>16</v>
-      </c>
-      <c r="L76" t="s">
-        <v>16</v>
-      </c>
-      <c r="M76" t="s">
-        <v>16</v>
-      </c>
-      <c r="N76" t="s">
+    <row r="142" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="C142" t="s">
+        <v>60</v>
+      </c>
+      <c r="D142" t="s">
+        <v>235</v>
+      </c>
+      <c r="E142" t="s">
+        <v>235</v>
+      </c>
+      <c r="F142" t="s">
+        <v>63</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H142" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="143" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F143" t="s">
+        <v>236</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H143" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="77" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F77" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H77" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="78" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F78" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I78" t="s">
-        <v>8</v>
-      </c>
-      <c r="J78" t="s">
-        <v>15</v>
-      </c>
-      <c r="K78" t="s">
-        <v>16</v>
-      </c>
-      <c r="L78" t="s">
-        <v>16</v>
-      </c>
-      <c r="M78" t="s">
-        <v>16</v>
-      </c>
-      <c r="N78" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="79" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F79" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H79" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="80" spans="6:15" x14ac:dyDescent="0.4">
-      <c r="F80" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H80" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="81" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C81" t="s">
-        <v>150</v>
-      </c>
-      <c r="D81" t="s">
-        <v>151</v>
-      </c>
-      <c r="E81" t="s">
-        <v>151</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G81" s="1"/>
-    </row>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-    </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="G83" s="1"/>
+    <row r="144" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F144" t="s">
+        <v>237</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I144" t="s">
+        <v>15</v>
+      </c>
+      <c r="J144" t="s">
+        <v>7</v>
+      </c>
+      <c r="K144" t="s">
+        <v>7</v>
+      </c>
+      <c r="L144" t="s">
+        <v>7</v>
+      </c>
+      <c r="M144" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F145" t="s">
+        <v>238</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I145" t="s">
+        <v>7</v>
+      </c>
+      <c r="J145" t="s">
+        <v>14</v>
+      </c>
+      <c r="K145" t="s">
+        <v>15</v>
+      </c>
+      <c r="L145" t="s">
+        <v>15</v>
+      </c>
+      <c r="M145" t="s">
+        <v>15</v>
+      </c>
+      <c r="N145" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="146" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F146" t="s">
+        <v>240</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H146" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="147" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F147" t="s">
+        <v>241</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I147" t="s">
+        <v>7</v>
+      </c>
+      <c r="J147" t="s">
+        <v>14</v>
+      </c>
+      <c r="K147" t="s">
+        <v>15</v>
+      </c>
+      <c r="L147" t="s">
+        <v>7</v>
+      </c>
+      <c r="M147" t="s">
+        <v>15</v>
+      </c>
+      <c r="N147" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="148" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F148" t="s">
+        <v>242</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="149" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F149" t="s">
+        <v>242</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I149" t="s">
+        <v>15</v>
+      </c>
+      <c r="J149" t="s">
+        <v>14</v>
+      </c>
+      <c r="K149" t="s">
+        <v>15</v>
+      </c>
+      <c r="L149" t="s">
+        <v>15</v>
+      </c>
+      <c r="M149" t="s">
+        <v>7</v>
+      </c>
+      <c r="N149" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="150" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="C150" t="s">
+        <v>243</v>
+      </c>
+      <c r="D150" t="s">
+        <v>244</v>
+      </c>
+      <c r="E150" t="s">
+        <v>245</v>
+      </c>
+      <c r="F150" t="s">
+        <v>246</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="151" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F151" t="s">
+        <v>247</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H151" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="152" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F152" t="s">
+        <v>248</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I152" t="s">
+        <v>15</v>
+      </c>
+      <c r="J152" t="s">
+        <v>14</v>
+      </c>
+      <c r="K152" t="s">
+        <v>15</v>
+      </c>
+      <c r="L152" t="s">
+        <v>15</v>
+      </c>
+      <c r="M152" t="s">
+        <v>15</v>
+      </c>
+      <c r="O152" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="153" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F153" t="s">
+        <v>77</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I153" t="s">
+        <v>15</v>
+      </c>
+      <c r="J153" t="s">
+        <v>14</v>
+      </c>
+      <c r="K153" t="s">
+        <v>15</v>
+      </c>
+      <c r="L153" t="s">
+        <v>15</v>
+      </c>
+      <c r="M153" t="s">
+        <v>15</v>
+      </c>
+      <c r="O153" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="154" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F154" t="s">
+        <v>250</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I154" t="s">
+        <v>15</v>
+      </c>
+      <c r="J154" t="s">
+        <v>14</v>
+      </c>
+      <c r="K154" t="s">
+        <v>15</v>
+      </c>
+      <c r="L154" t="s">
+        <v>15</v>
+      </c>
+      <c r="M154" t="s">
+        <v>15</v>
+      </c>
+      <c r="O154" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="155" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F155" t="s">
+        <v>251</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I155" t="s">
+        <v>15</v>
+      </c>
+      <c r="J155" t="s">
+        <v>14</v>
+      </c>
+      <c r="K155" t="s">
+        <v>15</v>
+      </c>
+      <c r="L155" t="s">
+        <v>7</v>
+      </c>
+      <c r="M155" t="s">
+        <v>15</v>
+      </c>
+      <c r="O155" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="156" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F156" t="s">
+        <v>252</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I156" t="s">
+        <v>15</v>
+      </c>
+      <c r="J156" t="s">
+        <v>14</v>
+      </c>
+      <c r="K156" t="s">
+        <v>15</v>
+      </c>
+      <c r="L156" t="s">
+        <v>7</v>
+      </c>
+      <c r="M156" t="s">
+        <v>15</v>
+      </c>
+      <c r="O156" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="157" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F157" t="s">
+        <v>253</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I157" t="s">
+        <v>15</v>
+      </c>
+      <c r="J157" t="s">
+        <v>14</v>
+      </c>
+      <c r="K157" t="s">
+        <v>15</v>
+      </c>
+      <c r="L157" t="s">
+        <v>15</v>
+      </c>
+      <c r="M157" t="s">
+        <v>15</v>
+      </c>
+      <c r="O157" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="158" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F158" t="s">
+        <v>254</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H158" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="159" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F159" t="s">
+        <v>255</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I159" t="s">
+        <v>15</v>
+      </c>
+      <c r="J159" t="s">
+        <v>14</v>
+      </c>
+      <c r="K159" t="s">
+        <v>15</v>
+      </c>
+      <c r="L159" t="s">
+        <v>7</v>
+      </c>
+      <c r="M159" t="s">
+        <v>7</v>
+      </c>
+      <c r="O159" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="160" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F160" t="s">
+        <v>257</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I160" t="s">
+        <v>7</v>
+      </c>
+      <c r="J160" t="s">
+        <v>14</v>
+      </c>
+      <c r="K160" t="s">
+        <v>7</v>
+      </c>
+      <c r="L160" t="s">
+        <v>7</v>
+      </c>
+      <c r="M160" t="s">
+        <v>7</v>
+      </c>
+      <c r="N160" t="s">
+        <v>258</v>
+      </c>
+      <c r="O160" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="161" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F161" t="s">
+        <v>260</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H161" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="162" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="C162" t="s">
+        <v>53</v>
+      </c>
+      <c r="D162" t="s">
+        <v>266</v>
+      </c>
+      <c r="E162" t="s">
+        <v>266</v>
+      </c>
+      <c r="F162" t="s">
+        <v>63</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H162" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="163" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F163" t="s">
+        <v>267</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I163" t="s">
+        <v>15</v>
+      </c>
+      <c r="J163" t="s">
+        <v>7</v>
+      </c>
+      <c r="K163" t="s">
+        <v>7</v>
+      </c>
+      <c r="L163" t="s">
+        <v>7</v>
+      </c>
+      <c r="M163" t="s">
+        <v>7</v>
+      </c>
+      <c r="O163" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="164" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F164" t="s">
+        <v>269</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I164" t="s">
+        <v>7</v>
+      </c>
+      <c r="J164" t="s">
+        <v>11</v>
+      </c>
+      <c r="K164" t="s">
+        <v>7</v>
+      </c>
+      <c r="L164" t="s">
+        <v>7</v>
+      </c>
+      <c r="M164" t="s">
+        <v>7</v>
+      </c>
+      <c r="O164" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="165" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="F165" t="s">
+        <v>270</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H165" t="s">
+        <v>94</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2717,84 +4945,256 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8B61166-5062-4DDB-95CE-36DBA430D25C}">
-  <dimension ref="B2:E8"/>
+  <dimension ref="B2:E18"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
         <v>49</v>
       </c>
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" t="s">
         <v>55</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s">
         <v>59</v>
       </c>
-      <c r="D7" t="s">
-        <v>60</v>
-      </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
         <v>149</v>
       </c>
-      <c r="D8" t="s">
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" t="s">
         <v>53</v>
       </c>
-      <c r="E8" t="s">
-        <v>152</v>
+      <c r="E9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>262</v>
+      </c>
+      <c r="C11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C13" t="s">
+        <v>271</v>
+      </c>
+      <c r="D13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E13" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" t="s">
+        <v>274</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>186</v>
+      </c>
+      <c r="C15" t="s">
+        <v>275</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16" t="s">
+        <v>276</v>
+      </c>
+      <c r="D16" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C17" t="s">
+        <v>278</v>
+      </c>
+      <c r="D17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" t="s">
+        <v>279</v>
+      </c>
+      <c r="D18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A160276A-4A25-4CCB-97DF-BFF009F5501A}">
+  <dimension ref="B2:D7"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
